--- a/usuarios.xlsx
+++ b/usuarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE43DBA3-23CF-4386-87EE-E5DBF050B242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB27398-A273-4540-AE7C-A818358170AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{F440FB22-D1F8-4AFF-9145-340B92143CBE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
   <si>
     <t>usuario</t>
   </si>
@@ -192,6 +192,12 @@
   </si>
   <si>
     <t>gestao</t>
+  </si>
+  <si>
+    <t>SubBrenda</t>
+  </si>
+  <si>
+    <t>SubLuma</t>
   </si>
 </sst>
 </file>
@@ -563,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E2D324-C034-4AA9-919B-38FE59BB4F47}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
@@ -1109,6 +1115,28 @@
         <v>50</v>
       </c>
     </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50">
+        <v>5072000</v>
+      </c>
+      <c r="C50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51">
+        <v>16111990</v>
+      </c>
+      <c r="C51" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{42E2D324-C034-4AA9-919B-38FE59BB4F47}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C45">

--- a/usuarios.xlsx
+++ b/usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB27398-A273-4540-AE7C-A818358170AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA936628-3020-4527-AB59-29305F15F5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{F440FB22-D1F8-4AFF-9145-340B92143CBE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="53">
   <si>
     <t>usuario</t>
   </si>
@@ -569,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E2D324-C034-4AA9-919B-38FE59BB4F47}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
@@ -1137,6 +1137,17 @@
         <v>52</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52">
+        <v>1616</v>
+      </c>
+      <c r="C52" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{42E2D324-C034-4AA9-919B-38FE59BB4F47}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C45">

--- a/usuarios.xlsx
+++ b/usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA936628-3020-4527-AB59-29305F15F5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E019867-2A20-4A89-A758-EE0C270B3235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{F440FB22-D1F8-4AFF-9145-340B92143CBE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="54">
   <si>
     <t>usuario</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>SubLuma</t>
+  </si>
+  <si>
+    <t>joao frutuoso machado neto</t>
   </si>
 </sst>
 </file>
@@ -569,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E2D324-C034-4AA9-919B-38FE59BB4F47}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
@@ -1148,6 +1151,17 @@
         <v>48</v>
       </c>
     </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53">
+        <v>1515</v>
+      </c>
+      <c r="C53" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{42E2D324-C034-4AA9-919B-38FE59BB4F47}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C45">
